--- a/data/trans_orig/P2A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17629</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22485</t>
+          <t>22720</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22219</t>
+          <t>21529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35569</t>
+          <t>36867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39656</t>
+          <t>39581</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>28444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39925</t>
+          <t>39840</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63302</t>
+          <t>62004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76652</t>
+          <t>77342</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>78,23%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18718</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31310</t>
+          <t>30893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23911</t>
+          <t>23777</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36904</t>
+          <t>36259</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46130</t>
+          <t>45761</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64340</t>
+          <t>64403</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,49%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>36994</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49169</t>
+          <t>49747</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28030</t>
+          <t>28675</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41023</t>
+          <t>41157</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68480</t>
+          <t>68417</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86690</t>
+          <t>87059</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12313</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24076</t>
+          <t>24192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13048</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27389</t>
+          <t>28062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43870</t>
+          <t>44739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40621</t>
+          <t>40505</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52384</t>
+          <t>52658</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42915</t>
+          <t>43556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54854</t>
+          <t>54783</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88730</t>
+          <t>87861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>105211</t>
+          <t>104538</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17856</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>30753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23234</t>
+          <t>22672</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36299</t>
+          <t>36656</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>45381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63285</t>
+          <t>63629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,59%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36167</t>
+          <t>35301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48198</t>
+          <t>47990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37217</t>
+          <t>36860</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50282</t>
+          <t>50844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76284</t>
+          <t>75940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95230</t>
+          <t>94188</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>67,49%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>55,05%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>77,38%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>15346</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24779</t>
+          <t>24573</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22561</t>
+          <t>22432</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36243</t>
+          <t>36715</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31239</t>
+          <t>31313</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40094</t>
+          <t>40153</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27492</t>
+          <t>27698</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38683</t>
+          <t>38528</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>62686</t>
+          <t>62214</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76368</t>
+          <t>76497</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27914</t>
+          <t>28661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43383</t>
+          <t>44147</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>33501</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48436</t>
+          <t>48856</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65120</t>
+          <t>64780</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88071</t>
+          <t>87678</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>67263</t>
+          <t>66499</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>82732</t>
+          <t>81985</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>62350</t>
+          <t>61930</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>78102</t>
+          <t>77285</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>133362</t>
+          <t>133755</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>156313</t>
+          <t>156653</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29619</t>
+          <t>29172</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44618</t>
+          <t>43537</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33134</t>
+          <t>32851</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47971</t>
+          <t>47875</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>66458</t>
+          <t>65761</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>87628</t>
+          <t>87781</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45549</t>
+          <t>46630</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60548</t>
+          <t>60995</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48606</t>
+          <t>48702</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63443</t>
+          <t>63726</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>99117</t>
+          <t>98964</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>120287</t>
+          <t>120984</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,79%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>149513</t>
+          <t>148119</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>182265</t>
+          <t>182107</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>179082</t>
+          <t>179464</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>213526</t>
+          <t>214454</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>338020</t>
+          <t>337770</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>386435</t>
+          <t>388260</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>321094</t>
+          <t>321252</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>353846</t>
+          <t>355240</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>315023</t>
+          <t>314095</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>349467</t>
+          <t>349085</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>645473</t>
+          <t>643648</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>693888</t>
+          <t>694138</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,27%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14424</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20228</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18523</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>30874</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10933</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17852</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28409</t>
+          <t>28895</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32140</t>
+          <t>32564</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44915</t>
+          <t>44533</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,2%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26017</t>
+          <t>25881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>27589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33888</t>
+          <t>33440</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49711</t>
+          <t>49846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28369</t>
+          <t>28505</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39849</t>
+          <t>40032</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30944</t>
+          <t>31297</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42889</t>
+          <t>43417</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63561</t>
+          <t>63426</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>79384</t>
+          <t>79832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,48%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14965</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26683</t>
+          <t>26440</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13824</t>
+          <t>13858</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25901</t>
+          <t>26037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31967</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48987</t>
+          <t>49235</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26030</t>
+          <t>26273</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37748</t>
+          <t>38157</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34033</t>
+          <t>33897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46110</t>
+          <t>46076</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>63660</t>
+          <t>63412</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80680</t>
+          <t>80367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14234</t>
+          <t>15154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25727</t>
+          <t>26303</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13648</t>
+          <t>13198</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26105</t>
+          <t>25600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31478</t>
+          <t>32412</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48827</t>
+          <t>50107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23953</t>
+          <t>23377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35446</t>
+          <t>34526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29367</t>
+          <t>29872</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41824</t>
+          <t>42274</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56325</t>
+          <t>55045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73674</t>
+          <t>72740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12216</t>
+          <t>12412</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>12127</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11324</t>
+          <t>10664</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22290</t>
+          <t>22005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12603</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20146</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20383</t>
+          <t>20668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31349</t>
+          <t>32009</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>75,01%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>12903</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23922</t>
+          <t>23969</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14584</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26260</t>
+          <t>26540</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30764</t>
+          <t>30243</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46712</t>
+          <t>46642</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20620</t>
+          <t>20573</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31468</t>
+          <t>31639</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23273</t>
+          <t>22993</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35029</t>
+          <t>34949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47363</t>
+          <t>47433</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63311</t>
+          <t>63832</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33160</t>
+          <t>33360</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51462</t>
+          <t>51616</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36421</t>
+          <t>36178</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54871</t>
+          <t>53913</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75094</t>
+          <t>74690</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100398</t>
+          <t>99518</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>65242</t>
+          <t>65088</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>83544</t>
+          <t>83344</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>66906</t>
+          <t>67864</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>85356</t>
+          <t>85599</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>138082</t>
+          <t>138962</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>163386</t>
+          <t>163790</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,68%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21795</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37219</t>
+          <t>36628</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32731</t>
+          <t>33265</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50500</t>
+          <t>49934</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>57838</t>
+          <t>58678</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82150</t>
+          <t>81669</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78320</t>
+          <t>78911</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93744</t>
+          <t>93513</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>79968</t>
+          <t>80534</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>97737</t>
+          <t>97203</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>163857</t>
+          <t>164338</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>188169</t>
+          <t>187329</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>153090</t>
+          <t>153097</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>187837</t>
+          <t>186219</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>172586</t>
+          <t>172497</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208284</t>
+          <t>208367</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>333641</t>
+          <t>333254</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>385221</t>
+          <t>384731</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>289128</t>
+          <t>290746</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>323875</t>
+          <t>323868</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>330497</t>
+          <t>330414</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>366195</t>
+          <t>366284</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>630525</t>
+          <t>631015</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>682105</t>
+          <t>682492</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24537</t>
+          <t>23834</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18571</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30833</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35468</t>
+          <t>35858</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51445</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,36%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20849</t>
+          <t>21552</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31726</t>
+          <t>31523</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21161</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33423</t>
+          <t>33721</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45935</t>
+          <t>45422</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61912</t>
+          <t>61522</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>21351</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18634</t>
+          <t>18532</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>31839</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42498</t>
+          <t>43316</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62191</t>
+          <t>63111</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35749</t>
+          <t>35724</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49230</t>
+          <t>49351</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47311</t>
+          <t>48156</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61361</t>
+          <t>61463</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88506</t>
+          <t>87586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108199</t>
+          <t>107381</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,26%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>11410</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23265</t>
+          <t>23105</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13285</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26049</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27825</t>
+          <t>27857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45446</t>
+          <t>44840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34848</t>
+          <t>35008</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46710</t>
+          <t>46703</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40128</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52892</t>
+          <t>52324</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78843</t>
+          <t>79449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>96464</t>
+          <t>96432</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,59%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23661</t>
+          <t>23431</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22701</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26968</t>
+          <t>26759</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42524</t>
+          <t>42575</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>21682</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32116</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24949</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>36164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50239</t>
+          <t>50188</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65795</t>
+          <t>66004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,15%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17266</t>
+          <t>17402</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18444</t>
+          <t>18762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20319</t>
+          <t>19878</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33425</t>
+          <t>32858</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,4%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15109</t>
+          <t>14973</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23985</t>
+          <t>23824</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>16754</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>26202</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34465</t>
+          <t>35032</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47571</t>
+          <t>48012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,72%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15597</t>
+          <t>15540</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>16565</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>16977</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28596</t>
+          <t>28954</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>11743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20175</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14565</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24493</t>
+          <t>23860</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30043</t>
+          <t>29685</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41831</t>
+          <t>41662</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25225</t>
+          <t>24645</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41065</t>
+          <t>40735</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26992</t>
+          <t>26991</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43287</t>
+          <t>43159</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56207</t>
+          <t>56673</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79125</t>
+          <t>79084</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75700</t>
+          <t>76030</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91540</t>
+          <t>92120</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>75836</t>
+          <t>75964</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>92131</t>
+          <t>92132</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>156763</t>
+          <t>156804</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>179681</t>
+          <t>179215</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33039</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50079</t>
+          <t>48599</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37087</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54393</t>
+          <t>54310</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74237</t>
+          <t>74248</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>98449</t>
+          <t>99074</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79574</t>
+          <t>81054</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96614</t>
+          <t>96681</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>84830</t>
+          <t>84913</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>102136</t>
+          <t>102245</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>170427</t>
+          <t>169802</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>194639</t>
+          <t>194628</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>163082</t>
+          <t>162427</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>198848</t>
+          <t>199215</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>173316</t>
+          <t>169476</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>207870</t>
+          <t>207926</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>342393</t>
+          <t>346326</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>393868</t>
+          <t>396908</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>326542</t>
+          <t>326175</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>362308</t>
+          <t>362963</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>363163</t>
+          <t>363107</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>397717</t>
+          <t>401557</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>702555</t>
+          <t>699515</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>754030</t>
+          <t>750097</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24421</t>
+          <t>24776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42792</t>
+          <t>43226</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>31333</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46765</t>
+          <t>47488</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60423</t>
+          <t>60373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85727</t>
+          <t>86629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,75%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30490</t>
+          <t>30056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48861</t>
+          <t>48506</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32601</t>
+          <t>31878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49048</t>
+          <t>48033</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66921</t>
+          <t>66019</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92225</t>
+          <t>92275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,45%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97076</t>
+          <t>97218</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118253</t>
+          <t>118758</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84594</t>
+          <t>86665</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108985</t>
+          <t>109554</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>188586</t>
+          <t>189233</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>223069</t>
+          <t>222963</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30578</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18611</t>
+          <t>18042</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43002</t>
+          <t>40931</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32181</t>
+          <t>32287</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66664</t>
+          <t>66017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36021</t>
+          <t>36182</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47190</t>
+          <t>47054</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44439</t>
+          <t>44428</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55857</t>
+          <t>56082</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85031</t>
+          <t>84808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100503</t>
+          <t>100723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,3%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11214</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22247</t>
+          <t>22086</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22724</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24928</t>
+          <t>24708</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40400</t>
+          <t>40623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43116</t>
+          <t>42692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57245</t>
+          <t>56353</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27425</t>
+          <t>24604</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57916</t>
+          <t>57004</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72610</t>
+          <t>69745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109206</t>
+          <t>108650</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27027</t>
+          <t>27451</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20218</t>
+          <t>21130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50709</t>
+          <t>53530</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39072</t>
+          <t>39628</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75668</t>
+          <t>78533</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>52,96%</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31172</t>
+          <t>31075</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32315</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40135</t>
+          <t>40131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65225</t>
+          <t>66024</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74030</t>
+          <t>74055</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25688</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35640</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34682</t>
+          <t>34182</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44926</t>
+          <t>44853</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63473</t>
+          <t>63672</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77991</t>
+          <t>78607</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20479</t>
+          <t>20304</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21504</t>
+          <t>22004</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>23746</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38880</t>
+          <t>38681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,79%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97550</t>
+          <t>97750</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>110982</t>
+          <t>111447</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110571</t>
+          <t>111817</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>137520</t>
+          <t>137844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216753</t>
+          <t>215586</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>245889</t>
+          <t>245856</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,64%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13061</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26958</t>
+          <t>26758</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45441</t>
+          <t>44195</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>34631</t>
+          <t>34664</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>63767</t>
+          <t>64934</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>107362</t>
+          <t>107796</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>119950</t>
+          <t>119934</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>125264</t>
+          <t>125631</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>141723</t>
+          <t>141720</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>238711</t>
+          <t>237850</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>258467</t>
+          <t>258227</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11669</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24257</t>
+          <t>23823</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15072</t>
+          <t>15075</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31531</t>
+          <t>31164</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29947</t>
+          <t>30187</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49703</t>
+          <t>50564</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>495054</t>
+          <t>494793</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>541281</t>
+          <t>542431</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>543841</t>
+          <t>545068</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>602518</t>
+          <t>601628</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1058540</t>
+          <t>1053870</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1130723</t>
+          <t>1125460</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>124874</t>
+          <t>123724</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>171101</t>
+          <t>171362</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>159454</t>
+          <t>160344</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>218131</t>
+          <t>216904</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>297404</t>
+          <t>302667</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>369587</t>
+          <t>374257</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
